--- a/artfynd/A 27827-2022 artfynd.xlsx
+++ b/artfynd/A 27827-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128184346</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
+        <v>56552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27827-2022 artfynd.xlsx
+++ b/artfynd/A 27827-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128184346</v>
       </c>
       <c r="B2" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27827-2022 artfynd.xlsx
+++ b/artfynd/A 27827-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128184346</v>
       </c>
       <c r="B2" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27827-2022 artfynd.xlsx
+++ b/artfynd/A 27827-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128184346</v>
+        <v>126404333</v>
       </c>
       <c r="B2" t="n">
-        <v>56583</v>
+        <v>43464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>201116</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SV om Kvarnmyren, Upl</t>
+          <t>Maran, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695072</v>
+        <v>695244</v>
       </c>
       <c r="R2" t="n">
-        <v>6664439</v>
+        <v>6664352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +770,320 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128184346</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SV om Kvarnmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>695072</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6664439</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Paulina Wietrzyk-Pelka</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Paulina Wietrzyk-Pelka</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131093246</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>19, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>695340</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6664318</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Ringbom, Alexandra Östberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131093251</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>14, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>695425</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6664285</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27827-2022 artfynd.xlsx
+++ b/artfynd/A 27827-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126404333</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128184346</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131093246</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131093251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>